--- a/InputData/trans/EVCC/EV Charger Cost.xlsx
+++ b/InputData/trans/EVCC/EV Charger Cost.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28512"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -17,7 +17,7 @@
     <sheet name="Data" sheetId="3" r:id="rId2"/>
     <sheet name="EVCC" sheetId="2" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -28,6 +28,9 @@
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -37,130 +40,130 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="42">
   <si>
+    <t>EVCC Electric Vehicle Charger Cost</t>
+  </si>
+  <si>
     <t>Source:</t>
   </si>
   <si>
+    <t>Costs</t>
+  </si>
+  <si>
+    <t>The National Academies Press</t>
+  </si>
+  <si>
+    <t>Assessment of Technologies for Improving Light-Duty Vehicle Fuel Economy 2025-2035</t>
+  </si>
+  <si>
+    <t>https://www.nap.edu/download/26092#</t>
+  </si>
+  <si>
+    <t>Tables 5.13, 5.14, and 5.15</t>
+  </si>
+  <si>
+    <t>Share of Chargers by Type</t>
+  </si>
+  <si>
     <t>U.S. Department of Energy</t>
   </si>
   <si>
+    <t>FOTW #1089, July 8, 2019: There are More Than 68,800 Electric Vehicle Charging Units in the United States</t>
+  </si>
+  <si>
+    <t>https://www.energy.gov/eere/vehicles/articles/fotw-1089-july-8-2019-there-are-more-68800-electric-vehicle-charging-units</t>
+  </si>
+  <si>
+    <t>Paragraph 1</t>
+  </si>
+  <si>
     <t>Notes</t>
   </si>
   <si>
+    <t>We take a weighted average of the costs of Fast DC and Level 2</t>
+  </si>
+  <si>
+    <t>chargers.  (We do not track level 1 chargers, which may be just</t>
+  </si>
+  <si>
+    <t>a standard electrical outlet in any home or business.)</t>
+  </si>
+  <si>
+    <t>To determine the costs for Fast DC and Level 2 capital and installation costs, we take</t>
+  </si>
+  <si>
+    <t xml:space="preserve">representative costs from the table (e.g. choosing </t>
+  </si>
+  <si>
+    <t>Currency Conversion</t>
+  </si>
+  <si>
+    <t>We assume the costs given in this document</t>
+  </si>
+  <si>
+    <t>are in 2020 dollars.  We convert to 2012 dollars via:</t>
+  </si>
+  <si>
+    <t>Capital Costs</t>
+  </si>
+  <si>
+    <t>EVSE Type</t>
+  </si>
+  <si>
+    <t>Low Est.</t>
+  </si>
+  <si>
+    <t>High Est.</t>
+  </si>
+  <si>
+    <t>Level 2 commercial</t>
+  </si>
+  <si>
+    <t>Average DCFC</t>
+  </si>
+  <si>
+    <t>Installation Costs</t>
+  </si>
+  <si>
+    <t>Avg. installation cost</t>
+  </si>
+  <si>
+    <t>Average Level 2</t>
+  </si>
+  <si>
+    <t>Average DCFC (150 kW taken as representative)</t>
+  </si>
+  <si>
+    <t>Chargers by Type</t>
+  </si>
+  <si>
+    <t>Number of chargers</t>
+  </si>
+  <si>
+    <t>Percent</t>
+  </si>
+  <si>
+    <t>Level 2</t>
+  </si>
+  <si>
+    <t>DCFC</t>
+  </si>
+  <si>
+    <t>Weighted Average Costs</t>
+  </si>
+  <si>
+    <t>Capital</t>
+  </si>
+  <si>
+    <t>Installation</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
     <t>Cap Cost</t>
   </si>
   <si>
     <t>EV Charger</t>
-  </si>
-  <si>
-    <t>EVSE Type</t>
-  </si>
-  <si>
-    <t>Level 2</t>
-  </si>
-  <si>
-    <t>DCFC</t>
-  </si>
-  <si>
-    <t>Low Est.</t>
-  </si>
-  <si>
-    <t>High Est.</t>
-  </si>
-  <si>
-    <t>Currency Conversion</t>
-  </si>
-  <si>
-    <t>EVCC Electric Vehicle Charger Cost</t>
-  </si>
-  <si>
-    <t>Capital Costs</t>
-  </si>
-  <si>
-    <t>Avg. installation cost</t>
-  </si>
-  <si>
-    <t>Installation Costs</t>
-  </si>
-  <si>
-    <t>Costs</t>
-  </si>
-  <si>
-    <t>Share of Chargers by Type</t>
-  </si>
-  <si>
-    <t>FOTW #1089, July 8, 2019: There are More Than 68,800 Electric Vehicle Charging Units in the United States</t>
-  </si>
-  <si>
-    <t>https://www.energy.gov/eere/vehicles/articles/fotw-1089-july-8-2019-there-are-more-68800-electric-vehicle-charging-units</t>
-  </si>
-  <si>
-    <t>Chargers by Type</t>
-  </si>
-  <si>
-    <t>Number of chargers</t>
-  </si>
-  <si>
-    <t>Percent</t>
-  </si>
-  <si>
-    <t>Paragraph 1</t>
-  </si>
-  <si>
-    <t>We take a weighted average of the costs of Fast DC and Level 2</t>
-  </si>
-  <si>
-    <t>chargers.  (We do not track level 1 chargers, which may be just</t>
-  </si>
-  <si>
-    <t>a standard electrical outlet in any home or business.)</t>
-  </si>
-  <si>
-    <t>Weighted Average Costs</t>
-  </si>
-  <si>
-    <t>Capital</t>
-  </si>
-  <si>
-    <t>Installation</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t>Level 2 commercial</t>
-  </si>
-  <si>
-    <t>The National Academies Press</t>
-  </si>
-  <si>
-    <t>Assessment of Technologies for Improving Light-Duty Vehicle Fuel Economy 2025-2035</t>
-  </si>
-  <si>
-    <t>https://www.nap.edu/download/26092#</t>
-  </si>
-  <si>
-    <t>Tables 5.13, 5.14, and 5.15</t>
-  </si>
-  <si>
-    <t>We assume the costs given in this document</t>
-  </si>
-  <si>
-    <t>are in 2020 dollars.  We convert to 2012 dollars via:</t>
-  </si>
-  <si>
-    <t>To determine the costs for Fast DC and Level 2 capital and installation costs, we take</t>
-  </si>
-  <si>
-    <t xml:space="preserve">representative costs from the table (e.g. choosing </t>
-  </si>
-  <si>
-    <t>Average DCFC</t>
-  </si>
-  <si>
-    <t>Average Level 2</t>
-  </si>
-  <si>
-    <t>Average DCFC (150 kW taken as representative)</t>
   </si>
 </sst>
 </file>
@@ -170,7 +173,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -664,125 +667,125 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="2" max="2" width="67.54296875" customWidth="1"/>
+    <col min="2" max="2" width="67.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="B4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
       <c r="B5" s="3">
         <v>2021</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2">
       <c r="B6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
       <c r="B7" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
       <c r="B8" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
       <c r="B10" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
       <c r="B11" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
       <c r="B12" s="3">
         <v>2019</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2">
       <c r="B13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="B14" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="B15" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B14" s="2" t="s">
+    <row r="27" spans="1:1">
+      <c r="A27" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B15" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A17" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A27" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
       <c r="A30">
         <v>0.88711067149387013</v>
       </c>
@@ -799,34 +802,34 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="13.453125" customWidth="1"/>
-    <col min="2" max="2" width="21.7265625" customWidth="1"/>
-    <col min="3" max="3" width="10.81640625" customWidth="1"/>
+    <col min="1" max="1" width="13.42578125" customWidth="1"/>
+    <col min="2" max="2" width="21.7109375" customWidth="1"/>
+    <col min="3" max="3" width="10.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3">
       <c r="A1" s="6" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B3">
         <v>2500</v>
@@ -835,9 +838,9 @@
         <v>4900</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="B4" s="5">
         <f>AVERAGE(20000,75600,128000)</f>
@@ -848,60 +851,60 @@
         <v>95266.666666666672</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3">
       <c r="A6" s="6" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="B8" s="5">
         <f>AVERAGE(4148,3039,2745,2837)</f>
         <v>3192.25</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="B9" s="5">
         <f>AVERAGE(47781,38047,28312,18577)</f>
         <v>33179.25</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3">
       <c r="A11" s="6" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="B13">
         <v>57940</v>
@@ -911,9 +914,9 @@
         <v>0.84215116279069768</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="B14">
         <v>10860</v>
@@ -923,34 +926,34 @@
         <v>0.15784883720930232</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3">
       <c r="A16" s="6" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="B17" s="5">
         <f>AVERAGE(B3:C3)*C13+AVERAGE(B4:C4)*C14</f>
         <v>16517.325581395347</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="B18" s="5">
         <f>B8*C13+B9*C14</f>
         <v>7925.6630813953489</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="B19" s="5">
         <f>SUM(B17:B18)</f>
@@ -970,20 +973,20 @@
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="12.1796875" customWidth="1"/>
-    <col min="2" max="2" width="15.26953125" customWidth="1"/>
+    <col min="1" max="1" width="12.140625" customWidth="1"/>
+    <col min="2" max="2" width="15.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2">
       <c r="B1" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="B2" s="5">
         <f>Data!B19</f>
@@ -993,4 +996,175 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009A9DAB439B36DB4795F39C4E722C7BC4" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="44674c89fa9bc5e97a878a6680c46188">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="79748b23-d81a-423e-9112-21109dc864e6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="447839a363ea5a12024b5bf1ab53ed90" ns2:_="">
+    <xsd:import namespace="79748b23-d81a-423e-9112-21109dc864e6"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="79748b23-d81a-423e-9112-21109dc864e6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C817D39C-F069-4C48-9156-FF59D8D502A8}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8D01EC05-74A8-4CBF-A799-16652CCC6D52}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D7AD1A8-3050-4819-AEAC-DA6836C2AA65}"/>
 </file>